--- a/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 39,34</t>
+          <t>14,01; 41,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 38,88</t>
+          <t>11,52; 38,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,29</t>
+          <t>0,0; 24,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 26,46</t>
+          <t>3,21; 25,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 29,51</t>
+          <t>5,76; 30,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 18,34</t>
+          <t>2,0; 17,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,62; 48,5</t>
+          <t>15,23; 46,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,29</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,78; 29,71</t>
+          <t>13,06; 30,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 23,46</t>
+          <t>8,32; 23,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 28,47</t>
+          <t>9,54; 28,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 15,5</t>
+          <t>3,62; 16,8</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 18,81</t>
+          <t>3,23; 18,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 16,35</t>
+          <t>3,08; 17,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 23,52</t>
+          <t>6,18; 23,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 18,84</t>
+          <t>3,17; 19,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 20,51</t>
+          <t>4,79; 22,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 29,54</t>
+          <t>9,81; 31,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 21,51</t>
+          <t>4,83; 21,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 24,04</t>
+          <t>6,89; 23,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,73</t>
+          <t>5,71; 16,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 20,62</t>
+          <t>7,16; 19,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 19,12</t>
+          <t>7,65; 19,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 19,23</t>
+          <t>6,66; 17,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 20,48</t>
+          <t>2,45; 20,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 26,44</t>
+          <t>5,52; 26,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,4</t>
+          <t>2,05; 18,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,81</t>
+          <t>1,6; 16,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 28,27</t>
+          <t>7,54; 28,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 20,48</t>
+          <t>3,65; 19,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 21,54</t>
+          <t>2,15; 22,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 23,21</t>
+          <t>4,69; 22,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,41</t>
+          <t>7,35; 20,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 18,48</t>
+          <t>6,5; 18,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 15,21</t>
+          <t>2,58; 15,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 16,08</t>
+          <t>4,28; 15,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 36,24</t>
+          <t>10,89; 38,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 15,62</t>
+          <t>2,16; 16,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 40,87</t>
+          <t>13,58; 39,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 18,55</t>
+          <t>1,98; 18,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 33,5</t>
+          <t>12,12; 34,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 25,78</t>
+          <t>6,71; 26,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 28,07</t>
+          <t>5,75; 28,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 16,32</t>
+          <t>1,71; 15,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 30,34</t>
+          <t>13,11; 30,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 17,37</t>
+          <t>5,79; 17,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,94; 30,13</t>
+          <t>12,39; 29,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,06</t>
+          <t>2,5; 12,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 22,33</t>
+          <t>10,7; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 17,45</t>
+          <t>8,13; 17,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 19,74</t>
+          <t>9,4; 19,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,78</t>
+          <t>4,38; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 21,39</t>
+          <t>11,84; 21,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,5</t>
+          <t>8,43; 17,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,01</t>
+          <t>9,65; 20,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,2</t>
+          <t>6,51; 15,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 19,96</t>
+          <t>12,68; 19,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,14</t>
+          <t>9,35; 15,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,7</t>
+          <t>10,78; 18,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,44</t>
+          <t>6,3; 12,63</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8281</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12762</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8776</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4599; 13527</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3624; 12198</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5937</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>829; 6620</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1652; 8807</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>689; 6098</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3682; 11170</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4559</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8030; 18738</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5483; 15294</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4630; 14066</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1936; 8991</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3724</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8545</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10680</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10406</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12561</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1347; 7796</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1264; 7188</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2639; 9943</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1403; 8656</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1977; 9143</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3955; 12545</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1989; 8780</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4398; 14838</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4741; 13673</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5824; 16188</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6411; 16161</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7199; 19347</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6082</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5861</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6455</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7990</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4098</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12537</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>616; 5034</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1818; 8720</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>567; 5162</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1234; 12653</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2650; 10088</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1314; 6932</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>599; 6188</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2671; 12572</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4432; 12519</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4481; 12668</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1429; 8467</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5735; 21152</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6466</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13724</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12618</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2796; 9945</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>901; 6860</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4451; 12844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>604; 5655</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4704; 13336</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3170; 12321</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1735; 8630</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>579; 5183</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8458; 19717</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5150; 15615</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7796; 18682</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1609; 8272</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17758</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17623</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18609</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42776</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13412; 26859</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11969; 25357</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11976; 25387</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7776; 23123</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17037; 31549</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13322; 27433</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11902; 25702</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11853; 27454</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>34147; 53489</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28536; 47421</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>27028; 45709</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>22666; 45449</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 41,22</t>
+          <t>13,72; 40,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 38,79</t>
+          <t>12,39; 38,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,37</t>
+          <t>0,0; 25,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 25,62</t>
+          <t>3,38; 25,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 30,71</t>
+          <t>7,23; 31,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,71</t>
+          <t>2,01; 18,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,23; 46,2</t>
+          <t>15,78; 49,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 17,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 30,47</t>
+          <t>12,31; 30,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 23,22</t>
+          <t>8,87; 24,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 28,98</t>
+          <t>9,64; 29,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,8</t>
+          <t>3,09; 17,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 18,72</t>
+          <t>4,65; 19,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 17,52</t>
+          <t>3,05; 17,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 23,29</t>
+          <t>5,98; 22,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 19,57</t>
+          <t>3,22; 17,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 22,14</t>
+          <t>4,82; 22,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 31,11</t>
+          <t>8,92; 29,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 21,34</t>
+          <t>4,82; 20,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 23,25</t>
+          <t>7,37; 23,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 16,48</t>
+          <t>5,62; 16,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 19,9</t>
+          <t>8,09; 20,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 19,27</t>
+          <t>7,55; 19,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 17,91</t>
+          <t>6,85; 18,92</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 20,01</t>
+          <t>2,42; 19,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 26,45</t>
+          <t>6,17; 26,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,69</t>
+          <t>2,08; 17,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 16,42</t>
+          <t>1,99; 16,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 28,72</t>
+          <t>7,99; 29,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 19,26</t>
+          <t>3,52; 19,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 22,25</t>
+          <t>2,03; 20,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 22,09</t>
+          <t>5,15; 22,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 20,77</t>
+          <t>6,71; 20,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 18,37</t>
+          <t>6,51; 18,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 15,28</t>
+          <t>2,88; 15,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,79</t>
+          <t>4,15; 15,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 38,73</t>
+          <t>9,38; 35,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 16,42</t>
+          <t>2,18; 15,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 39,17</t>
+          <t>13,57; 41,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 18,5</t>
+          <t>1,91; 17,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 34,36</t>
+          <t>12,64; 34,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 26,09</t>
+          <t>7,28; 25,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 28,63</t>
+          <t>4,98; 28,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,33</t>
+          <t>1,72; 15,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 30,57</t>
+          <t>13,82; 30,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,54</t>
+          <t>5,43; 17,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 29,68</t>
+          <t>11,4; 29,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 12,85</t>
+          <t>2,79; 12,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 21,43</t>
+          <t>10,34; 21,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,22</t>
+          <t>8,3; 17,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 19,92</t>
+          <t>9,27; 19,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,01</t>
+          <t>4,38; 12,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 21,92</t>
+          <t>11,59; 21,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,37</t>
+          <t>8,94; 18,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,85</t>
+          <t>9,82; 20,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,07</t>
+          <t>6,53; 15,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 19,87</t>
+          <t>12,26; 19,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,54</t>
+          <t>9,49; 15,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 18,23</t>
+          <t>10,9; 18,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,63</t>
+          <t>6,62; 12,52</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4599; 13527</t>
+          <t>4503; 13211</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3624; 12198</t>
+          <t>3895; 12099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5937</t>
+          <t>0; 6290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>829; 6620</t>
+          <t>874; 6652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1652; 8807</t>
+          <t>2075; 8892</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>689; 6098</t>
+          <t>693; 6412</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3682; 11170</t>
+          <t>3816; 11875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 4705</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8030; 18738</t>
+          <t>7569; 18903</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5483; 15294</t>
+          <t>5846; 15923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4630; 14066</t>
+          <t>4680; 14462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1936; 8991</t>
+          <t>1652; 9110</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1347; 7796</t>
+          <t>1937; 8250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1264; 7188</t>
+          <t>1251; 7251</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2639; 9943</t>
+          <t>2554; 9412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1403; 8656</t>
+          <t>1426; 7876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1977; 9143</t>
+          <t>1992; 9259</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3955; 12545</t>
+          <t>3597; 11995</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1989; 8780</t>
+          <t>1984; 8543</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4398; 14838</t>
+          <t>4701; 14856</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4741; 13673</t>
+          <t>4660; 14025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5824; 16188</t>
+          <t>6580; 16522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6411; 16161</t>
+          <t>6333; 16396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7199; 19347</t>
+          <t>7396; 20445</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>616; 5034</t>
+          <t>609; 4989</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1818; 8720</t>
+          <t>2035; 8670</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>567; 5162</t>
+          <t>573; 4926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1234; 12653</t>
+          <t>1530; 12610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2650; 10088</t>
+          <t>2808; 10365</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1314; 6932</t>
+          <t>1267; 6925</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>599; 6188</t>
+          <t>564; 5696</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2671; 12572</t>
+          <t>2929; 12597</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4432; 12519</t>
+          <t>4044; 12553</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4481; 12668</t>
+          <t>4491; 12815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1429; 8467</t>
+          <t>1594; 8371</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5735; 21152</t>
+          <t>5560; 20681</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2796; 9945</t>
+          <t>2407; 9241</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>901; 6860</t>
+          <t>912; 6516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4451; 12844</t>
+          <t>4449; 13482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>604; 5655</t>
+          <t>583; 5320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4704; 13336</t>
+          <t>4906; 13441</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3170; 12321</t>
+          <t>3438; 11980</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1735; 8630</t>
+          <t>1501; 8522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>579; 5183</t>
+          <t>581; 5211</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8458; 19717</t>
+          <t>8913; 19586</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5150; 15615</t>
+          <t>4832; 15150</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7796; 18682</t>
+          <t>7174; 18267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1609; 8272</t>
+          <t>1795; 8209</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13412; 26859</t>
+          <t>12958; 26910</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11969; 25357</t>
+          <t>12225; 25543</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11976; 25387</t>
+          <t>11815; 24797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7776; 23123</t>
+          <t>7779; 22522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17037; 31549</t>
+          <t>16676; 31017</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13322; 27433</t>
+          <t>14124; 28594</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11902; 25702</t>
+          <t>12105; 25464</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11853; 27454</t>
+          <t>11891; 27497</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34147; 53489</t>
+          <t>32995; 52511</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28536; 47421</t>
+          <t>28961; 47480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27028; 45709</t>
+          <t>27336; 45555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22666; 45449</t>
+          <t>23828; 45074</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,23%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22,72%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,93%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 40,26</t>
+          <t>7,1; 29,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 38,48</t>
+          <t>1,98; 18,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,82</t>
+          <t>15,62; 48,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 25,74</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 31,01</t>
+          <t>14,74; 39,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,63</t>
+          <t>11,13; 38,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 49,12</t>
+          <t>0,0; 23,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,01</t>
+          <t>3,51; 27,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 30,74</t>
+          <t>12,78; 29,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 24,17</t>
+          <t>8,57; 23,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 29,8</t>
+          <t>9,62; 28,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,03</t>
+          <t>3,68; 16,99</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>13,46%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 19,81</t>
+          <t>4,61; 20,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 17,68</t>
+          <t>9,14; 29,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 22,04</t>
+          <t>4,82; 21,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 17,8</t>
+          <t>7,13; 23,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 22,42</t>
+          <t>3,23; 18,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 29,75</t>
+          <t>3,08; 16,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 20,76</t>
+          <t>6,38; 23,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 23,28</t>
+          <t>4,03; 22,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,91</t>
+          <t>5,54; 16,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 20,31</t>
+          <t>7,72; 20,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 19,55</t>
+          <t>7,78; 19,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 18,92</t>
+          <t>7,63; 19,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,85%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 19,83</t>
+          <t>7,55; 28,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 26,3</t>
+          <t>4,03; 20,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 17,84</t>
+          <t>2,12; 21,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,36</t>
+          <t>5,6; 24,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 29,51</t>
+          <t>2,44; 20,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 19,24</t>
+          <t>6,28; 26,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 20,48</t>
+          <t>2,06; 18,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 22,13</t>
+          <t>5,84; 23,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 20,82</t>
+          <t>7,27; 21,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 18,58</t>
+          <t>6,2; 18,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 15,1</t>
+          <t>2,79; 15,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,43</t>
+          <t>6,76; 19,81</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>25,04%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 35,99</t>
+          <t>11,64; 33,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 15,59</t>
+          <t>6,85; 25,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 41,12</t>
+          <t>6,77; 28,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,41</t>
+          <t>1,6; 15,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 34,63</t>
+          <t>8,68; 36,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 25,36</t>
+          <t>1,49; 15,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 28,27</t>
+          <t>12,85; 40,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,41</t>
+          <t>1,78; 18,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 30,37</t>
+          <t>13,71; 30,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 17,02</t>
+          <t>5,42; 17,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 29,03</t>
+          <t>11,94; 30,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,75</t>
+          <t>2,6; 13,01</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,48</t>
+          <t>11,61; 21,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,35</t>
+          <t>8,66; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,45</t>
+          <t>10,39; 21,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,67</t>
+          <t>6,71; 15,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,55</t>
+          <t>10,94; 22,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,1</t>
+          <t>8,09; 17,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,66</t>
+          <t>9,42; 19,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,09</t>
+          <t>6,81; 16,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,5</t>
+          <t>12,64; 19,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,56</t>
+          <t>9,27; 16,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 18,17</t>
+          <t>11,03; 19,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,52</t>
+          <t>7,77; 13,8</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>8281</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7144</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1782</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4533</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4503; 13211</t>
+          <t>2035; 8463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3895; 12099</t>
+          <t>681; 6314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6290</t>
+          <t>3775; 11726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>874; 6652</t>
+          <t>0; 3909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2075; 8892</t>
+          <t>4836; 12910</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>693; 6412</t>
+          <t>3501; 12225</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3816; 11875</t>
+          <t>0; 5674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4705</t>
+          <t>925; 7293</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7569; 18903</t>
+          <t>7862; 18268</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5846; 15923</t>
+          <t>5643; 15455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4680; 14462</t>
+          <t>4672; 13818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1652; 9110</t>
+          <t>1873; 8651</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3942</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3261</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5745</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7419</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4660</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11667</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1937; 8250</t>
+          <t>1903; 8473</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1251; 7251</t>
+          <t>3687; 11909</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2554; 9412</t>
+          <t>1984; 8851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1426; 7876</t>
+          <t>4028; 12989</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1992; 9259</t>
+          <t>1345; 7833</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3597; 11995</t>
+          <t>1264; 6709</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1984; 8543</t>
+          <t>2726; 10043</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4701; 14856</t>
+          <t>1456; 8063</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4660; 14025</t>
+          <t>4596; 13875</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6580; 16522</t>
+          <t>6281; 16772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6333; 16396</t>
+          <t>6524; 16029</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7396; 20445</t>
+          <t>7064; 18474</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5861</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6159</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4567</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6082</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5861</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3423</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12503</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>609; 4989</t>
+          <t>2651; 9929</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2035; 8670</t>
+          <t>1449; 7371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>573; 4926</t>
+          <t>590; 5989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1530; 12610</t>
+          <t>2932; 12787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2808; 10365</t>
+          <t>615; 5153</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1267; 6925</t>
+          <t>2069; 8717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>564; 5696</t>
+          <t>568; 5082</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2929; 12597</t>
+          <t>2967; 11960</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4044; 12553</t>
+          <t>4380; 12905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4491; 12815</t>
+          <t>4278; 12743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1594; 8371</t>
+          <t>1546; 8428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5560; 20681</t>
+          <t>6970; 20441</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6466</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5258</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2786</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8211</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6466</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4407</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3872</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2407; 9241</t>
+          <t>4520; 13005</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>912; 6516</t>
+          <t>3236; 12175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4449; 13482</t>
+          <t>2040; 8462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>583; 5320</t>
+          <t>505; 4870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4906; 13441</t>
+          <t>2229; 9306</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3438; 11980</t>
+          <t>623; 6528</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1501; 8522</t>
+          <t>4214; 13399</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>581; 5211</t>
+          <t>531; 5614</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8913; 19586</t>
+          <t>8844; 19566</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4832; 15150</t>
+          <t>4821; 15458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7174; 18267</t>
+          <t>7514; 18960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1795; 8209</t>
+          <t>1593; 7970</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12958; 26910</t>
+          <t>16713; 30782</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12225; 25543</t>
+          <t>13676; 27640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11815; 24797</t>
+          <t>12814; 25905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7779; 22522</t>
+          <t>11064; 25466</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16676; 31017</t>
+          <t>13711; 27978</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14124; 28594</t>
+          <t>11906; 25693</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12105; 25464</t>
+          <t>12002; 25156</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11891; 27497</t>
+          <t>9733; 23447</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32995; 52511</t>
+          <t>34029; 53746</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28961; 47480</t>
+          <t>28283; 49257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27336; 45555</t>
+          <t>27656; 49384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23828; 45074</t>
+          <t>23936; 42490</t>
         </is>
       </c>
     </row>
